--- a/test-data/bulk-frontend-test-users-250.xlsx
+++ b/test-data/bulk-frontend-test-users-250.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABHINAV TEJA\Downloads\module8-SM\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F756AD7-CC7C-48A1-8B75-826FCB2BCA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FDAC38-FB43-49E0-9D00-6F747BBBEA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="11466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="11466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="People import" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="766">
   <si>
     <t>email</t>
   </si>
@@ -2266,315 +2266,6 @@
   </si>
   <si>
     <t>CSETEST260210</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty01@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Diya Sharma</t>
-  </si>
-  <si>
-    <t>8000000301</t>
-  </si>
-  <si>
-    <t>faculty</t>
-  </si>
-  <si>
-    <t>research</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty02@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Kabir Sharma</t>
-  </si>
-  <si>
-    <t>8000000302</t>
-  </si>
-  <si>
-    <t>crcs_self</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty03@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Meera Sharma</t>
-  </si>
-  <si>
-    <t>8000000303</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty04@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Arjun Sharma</t>
-  </si>
-  <si>
-    <t>8000000304</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty05@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Anaya Sharma</t>
-  </si>
-  <si>
-    <t>8000000305</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty06@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Vihaan Sharma</t>
-  </si>
-  <si>
-    <t>8000000306</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty07@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Isha Sharma</t>
-  </si>
-  <si>
-    <t>8000000307</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty08@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Rohan Sharma</t>
-  </si>
-  <si>
-    <t>8000000308</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty09@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Nisha Sharma</t>
-  </si>
-  <si>
-    <t>8000000309</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty10@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Aarav Reddy</t>
-  </si>
-  <si>
-    <t>8000000310</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty11@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Diya Reddy</t>
-  </si>
-  <si>
-    <t>8000000311</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty12@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Kabir Reddy</t>
-  </si>
-  <si>
-    <t>8000000312</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty13@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Meera Reddy</t>
-  </si>
-  <si>
-    <t>8000000313</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty14@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Arjun Reddy</t>
-  </si>
-  <si>
-    <t>8000000314</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty15@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Anaya Reddy</t>
-  </si>
-  <si>
-    <t>8000000315</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty16@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Vihaan Reddy</t>
-  </si>
-  <si>
-    <t>8000000316</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty17@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Isha Reddy</t>
-  </si>
-  <si>
-    <t>8000000317</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty18@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Rohan Reddy</t>
-  </si>
-  <si>
-    <t>8000000318</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty19@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Nisha Reddy</t>
-  </si>
-  <si>
-    <t>8000000319</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty20@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Aarav Kumar</t>
-  </si>
-  <si>
-    <t>8000000320</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty21@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Diya Kumar</t>
-  </si>
-  <si>
-    <t>8000000321</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty22@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Kabir Kumar</t>
-  </si>
-  <si>
-    <t>8000000322</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty23@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Meera Kumar</t>
-  </si>
-  <si>
-    <t>8000000323</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty24@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Arjun Kumar</t>
-  </si>
-  <si>
-    <t>8000000324</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-faculty25@example.edu</t>
-  </si>
-  <si>
-    <t>Dr Anaya Kumar</t>
-  </si>
-  <si>
-    <t>8000000325</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator01@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Diya Sharma</t>
-  </si>
-  <si>
-    <t>8000000401</t>
-  </si>
-  <si>
-    <t>faculty_coordinator</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator02@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Kabir Sharma</t>
-  </si>
-  <si>
-    <t>8000000402</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator03@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Meera Sharma</t>
-  </si>
-  <si>
-    <t>8000000403</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator04@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Arjun Sharma</t>
-  </si>
-  <si>
-    <t>8000000404</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator05@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Anaya Sharma</t>
-  </si>
-  <si>
-    <t>8000000405</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator06@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Vihaan Sharma</t>
-  </si>
-  <si>
-    <t>8000000406</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator07@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Isha Sharma</t>
-  </si>
-  <si>
-    <t>8000000407</t>
-  </si>
-  <si>
-    <t>bulk-test-20260911-coordinator08@example.edu</t>
-  </si>
-  <si>
-    <t>Coordinator Rohan Sharma</t>
-  </si>
-  <si>
-    <t>8000000408</t>
   </si>
   <si>
     <t>Test workbook summary</t>
@@ -3008,8 +2699,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J244"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:J211"/>
+  <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="48.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3023,7 +2714,7 @@
     <col min="10" max="10" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3055,7 +2746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3087,7 +2778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -3119,7 +2810,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3151,7 +2842,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -3183,7 +2874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -3215,7 +2906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -3247,7 +2938,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -3279,7 +2970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -3311,7 +3002,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -3343,7 +3034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -3375,7 +3066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -3407,7 +3098,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -3439,7 +3130,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -3471,7 +3162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -3503,7 +3194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -3535,7 +3226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -3567,7 +3258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -3599,7 +3290,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -3631,7 +3322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>89</v>
       </c>
@@ -3663,7 +3354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -3695,7 +3386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -3727,7 +3418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>101</v>
       </c>
@@ -3759,7 +3450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -3791,7 +3482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>109</v>
       </c>
@@ -3823,7 +3514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -3855,7 +3546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -3887,7 +3578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -3919,7 +3610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>125</v>
       </c>
@@ -3951,7 +3642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>129</v>
       </c>
@@ -3983,7 +3674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>133</v>
       </c>
@@ -4015,7 +3706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>137</v>
       </c>
@@ -4047,7 +3738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>141</v>
       </c>
@@ -4079,7 +3770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>145</v>
       </c>
@@ -4111,7 +3802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>149</v>
       </c>
@@ -4143,7 +3834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>153</v>
       </c>
@@ -4175,7 +3866,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>157</v>
       </c>
@@ -4207,7 +3898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>161</v>
       </c>
@@ -4239,7 +3930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>165</v>
       </c>
@@ -4271,7 +3962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>169</v>
       </c>
@@ -4303,7 +3994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>173</v>
       </c>
@@ -4335,7 +4026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>177</v>
       </c>
@@ -4367,7 +4058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>181</v>
       </c>
@@ -4399,7 +4090,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>185</v>
       </c>
@@ -4431,7 +4122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>189</v>
       </c>
@@ -4463,7 +4154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>193</v>
       </c>
@@ -4495,7 +4186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>197</v>
       </c>
@@ -4527,7 +4218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>201</v>
       </c>
@@ -4559,7 +4250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>205</v>
       </c>
@@ -4591,7 +4282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>209</v>
       </c>
@@ -4623,7 +4314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>213</v>
       </c>
@@ -4655,7 +4346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>217</v>
       </c>
@@ -4687,7 +4378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>221</v>
       </c>
@@ -4719,7 +4410,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>225</v>
       </c>
@@ -4751,7 +4442,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>229</v>
       </c>
@@ -4783,7 +4474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>233</v>
       </c>
@@ -4815,7 +4506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>237</v>
       </c>
@@ -4847,7 +4538,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>241</v>
       </c>
@@ -4879,7 +4570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>245</v>
       </c>
@@ -4911,7 +4602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>249</v>
       </c>
@@ -4943,7 +4634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>253</v>
       </c>
@@ -4975,7 +4666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>257</v>
       </c>
@@ -5007,7 +4698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>261</v>
       </c>
@@ -5039,7 +4730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>265</v>
       </c>
@@ -5071,7 +4762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>269</v>
       </c>
@@ -5103,7 +4794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>273</v>
       </c>
@@ -5135,7 +4826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>277</v>
       </c>
@@ -5167,7 +4858,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>281</v>
       </c>
@@ -5199,7 +4890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>285</v>
       </c>
@@ -5231,7 +4922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>289</v>
       </c>
@@ -5263,7 +4954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>293</v>
       </c>
@@ -5295,7 +4986,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>297</v>
       </c>
@@ -5327,7 +5018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>301</v>
       </c>
@@ -5359,7 +5050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>305</v>
       </c>
@@ -5391,7 +5082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>309</v>
       </c>
@@ -5423,7 +5114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>313</v>
       </c>
@@ -5455,7 +5146,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>317</v>
       </c>
@@ -5487,7 +5178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>321</v>
       </c>
@@ -5519,7 +5210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>325</v>
       </c>
@@ -5551,7 +5242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>329</v>
       </c>
@@ -5583,7 +5274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>333</v>
       </c>
@@ -5615,7 +5306,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>337</v>
       </c>
@@ -5647,7 +5338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>341</v>
       </c>
@@ -5679,7 +5370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>345</v>
       </c>
@@ -5711,7 +5402,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>349</v>
       </c>
@@ -5743,7 +5434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>353</v>
       </c>
@@ -5775,7 +5466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>357</v>
       </c>
@@ -5807,7 +5498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>361</v>
       </c>
@@ -5839,7 +5530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>365</v>
       </c>
@@ -5871,7 +5562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>369</v>
       </c>
@@ -5903,7 +5594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>373</v>
       </c>
@@ -5935,7 +5626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>377</v>
       </c>
@@ -5967,7 +5658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>381</v>
       </c>
@@ -5999,7 +5690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>385</v>
       </c>
@@ -6031,7 +5722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>389</v>
       </c>
@@ -6063,7 +5754,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>393</v>
       </c>
@@ -6095,7 +5786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>397</v>
       </c>
@@ -6127,7 +5818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>401</v>
       </c>
@@ -6159,7 +5850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>405</v>
       </c>
@@ -6191,7 +5882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>409</v>
       </c>
@@ -6223,7 +5914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>413</v>
       </c>
@@ -6255,7 +5946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>417</v>
       </c>
@@ -6287,7 +5978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>420</v>
       </c>
@@ -6319,7 +6010,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>423</v>
       </c>
@@ -6351,7 +6042,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>426</v>
       </c>
@@ -6383,7 +6074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>429</v>
       </c>
@@ -6415,7 +6106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>432</v>
       </c>
@@ -6447,7 +6138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>435</v>
       </c>
@@ -6479,7 +6170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>438</v>
       </c>
@@ -6511,7 +6202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>441</v>
       </c>
@@ -6543,7 +6234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>444</v>
       </c>
@@ -6575,7 +6266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>447</v>
       </c>
@@ -6607,7 +6298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>450</v>
       </c>
@@ -6639,7 +6330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>453</v>
       </c>
@@ -6671,7 +6362,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>456</v>
       </c>
@@ -6703,7 +6394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>459</v>
       </c>
@@ -6735,7 +6426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>462</v>
       </c>
@@ -6767,7 +6458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>465</v>
       </c>
@@ -6799,7 +6490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>468</v>
       </c>
@@ -6831,7 +6522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>471</v>
       </c>
@@ -6863,7 +6554,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>474</v>
       </c>
@@ -6895,7 +6586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>477</v>
       </c>
@@ -6927,7 +6618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>480</v>
       </c>
@@ -6959,7 +6650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>483</v>
       </c>
@@ -6991,7 +6682,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>486</v>
       </c>
@@ -7023,7 +6714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>489</v>
       </c>
@@ -7055,7 +6746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>492</v>
       </c>
@@ -7087,7 +6778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>495</v>
       </c>
@@ -7119,7 +6810,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>498</v>
       </c>
@@ -7151,7 +6842,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>501</v>
       </c>
@@ -7183,7 +6874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>504</v>
       </c>
@@ -7215,7 +6906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>507</v>
       </c>
@@ -7247,7 +6938,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>510</v>
       </c>
@@ -7279,7 +6970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>513</v>
       </c>
@@ -7311,7 +7002,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>516</v>
       </c>
@@ -7343,7 +7034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>519</v>
       </c>
@@ -7375,7 +7066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>522</v>
       </c>
@@ -7407,7 +7098,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>525</v>
       </c>
@@ -7439,7 +7130,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>528</v>
       </c>
@@ -7471,7 +7162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>531</v>
       </c>
@@ -7503,7 +7194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>534</v>
       </c>
@@ -7535,7 +7226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>537</v>
       </c>
@@ -7567,7 +7258,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>540</v>
       </c>
@@ -7599,7 +7290,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>543</v>
       </c>
@@ -7631,7 +7322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>546</v>
       </c>
@@ -7663,7 +7354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>549</v>
       </c>
@@ -7695,7 +7386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>552</v>
       </c>
@@ -7727,7 +7418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>555</v>
       </c>
@@ -7759,7 +7450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>558</v>
       </c>
@@ -7791,7 +7482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>561</v>
       </c>
@@ -7823,7 +7514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>564</v>
       </c>
@@ -7855,7 +7546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>567</v>
       </c>
@@ -7887,7 +7578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>570</v>
       </c>
@@ -7919,7 +7610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>573</v>
       </c>
@@ -7951,7 +7642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>576</v>
       </c>
@@ -7983,7 +7674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>579</v>
       </c>
@@ -8015,7 +7706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>582</v>
       </c>
@@ -8047,7 +7738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>585</v>
       </c>
@@ -8079,7 +7770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>588</v>
       </c>
@@ -8111,7 +7802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>591</v>
       </c>
@@ -8143,7 +7834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>594</v>
       </c>
@@ -8175,7 +7866,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>597</v>
       </c>
@@ -8207,7 +7898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>600</v>
       </c>
@@ -8239,7 +7930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>603</v>
       </c>
@@ -8271,7 +7962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>606</v>
       </c>
@@ -8303,7 +7994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>609</v>
       </c>
@@ -8335,7 +8026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>612</v>
       </c>
@@ -8367,7 +8058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" t="s">
         <v>615</v>
       </c>
@@ -8399,7 +8090,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" t="s">
         <v>618</v>
       </c>
@@ -8431,7 +8122,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" t="s">
         <v>621</v>
       </c>
@@ -8463,7 +8154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" t="s">
         <v>624</v>
       </c>
@@ -8495,7 +8186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" t="s">
         <v>627</v>
       </c>
@@ -8527,7 +8218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" t="s">
         <v>630</v>
       </c>
@@ -8559,7 +8250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" t="s">
         <v>633</v>
       </c>
@@ -8591,7 +8282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" t="s">
         <v>636</v>
       </c>
@@ -8623,7 +8314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" t="s">
         <v>639</v>
       </c>
@@ -8655,7 +8346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" t="s">
         <v>642</v>
       </c>
@@ -8687,7 +8378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" t="s">
         <v>645</v>
       </c>
@@ -8719,7 +8410,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" t="s">
         <v>648</v>
       </c>
@@ -8751,7 +8442,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" t="s">
         <v>651</v>
       </c>
@@ -8783,7 +8474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" t="s">
         <v>654</v>
       </c>
@@ -8815,7 +8506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" t="s">
         <v>657</v>
       </c>
@@ -8847,7 +8538,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" t="s">
         <v>660</v>
       </c>
@@ -8879,7 +8570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" t="s">
         <v>663</v>
       </c>
@@ -8911,7 +8602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" t="s">
         <v>666</v>
       </c>
@@ -8943,7 +8634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" t="s">
         <v>669</v>
       </c>
@@ -8975,7 +8666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" t="s">
         <v>672</v>
       </c>
@@ -9007,7 +8698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" t="s">
         <v>675</v>
       </c>
@@ -9039,7 +8730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" t="s">
         <v>678</v>
       </c>
@@ -9071,7 +8762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" t="s">
         <v>681</v>
       </c>
@@ -9103,7 +8794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" t="s">
         <v>684</v>
       </c>
@@ -9135,7 +8826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" t="s">
         <v>687</v>
       </c>
@@ -9167,7 +8858,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" t="s">
         <v>690</v>
       </c>
@@ -9199,7 +8890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" t="s">
         <v>693</v>
       </c>
@@ -9231,7 +8922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" t="s">
         <v>696</v>
       </c>
@@ -9263,7 +8954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" t="s">
         <v>699</v>
       </c>
@@ -9295,7 +8986,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" t="s">
         <v>702</v>
       </c>
@@ -9327,7 +9018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" t="s">
         <v>705</v>
       </c>
@@ -9359,7 +9050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" t="s">
         <v>708</v>
       </c>
@@ -9391,7 +9082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" t="s">
         <v>711</v>
       </c>
@@ -9423,7 +9114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" t="s">
         <v>714</v>
       </c>
@@ -9455,7 +9146,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" t="s">
         <v>717</v>
       </c>
@@ -9487,7 +9178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" t="s">
         <v>720</v>
       </c>
@@ -9519,7 +9210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" t="s">
         <v>723</v>
       </c>
@@ -9551,7 +9242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" t="s">
         <v>726</v>
       </c>
@@ -9583,7 +9274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" t="s">
         <v>729</v>
       </c>
@@ -9615,7 +9306,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" t="s">
         <v>732</v>
       </c>
@@ -9647,7 +9338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" t="s">
         <v>735</v>
       </c>
@@ -9679,7 +9370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" t="s">
         <v>738</v>
       </c>
@@ -9711,7 +9402,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" t="s">
         <v>741</v>
       </c>
@@ -9743,7 +9434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" t="s">
         <v>744</v>
       </c>
@@ -9773,1069 +9464,13 @@
       </c>
       <c r="J211" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A212" t="s">
-        <v>747</v>
-      </c>
-      <c r="B212" t="s">
-        <v>11</v>
-      </c>
-      <c r="C212" t="s">
-        <v>748</v>
-      </c>
-      <c r="D212" t="s">
-        <v>749</v>
-      </c>
-      <c r="E212" t="s">
-        <v>750</v>
-      </c>
-      <c r="F212" t="s">
-        <v>15</v>
-      </c>
-      <c r="G212" t="s">
-        <v>16</v>
-      </c>
-      <c r="H212" t="s">
-        <v>16</v>
-      </c>
-      <c r="I212" t="s">
-        <v>16</v>
-      </c>
-      <c r="J212" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="213" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A213" t="s">
-        <v>752</v>
-      </c>
-      <c r="B213" t="s">
-        <v>11</v>
-      </c>
-      <c r="C213" t="s">
-        <v>753</v>
-      </c>
-      <c r="D213" t="s">
-        <v>754</v>
-      </c>
-      <c r="E213" t="s">
-        <v>750</v>
-      </c>
-      <c r="F213" t="s">
-        <v>15</v>
-      </c>
-      <c r="G213" t="s">
-        <v>16</v>
-      </c>
-      <c r="H213" t="s">
-        <v>16</v>
-      </c>
-      <c r="I213" t="s">
-        <v>16</v>
-      </c>
-      <c r="J213" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A214" t="s">
-        <v>756</v>
-      </c>
-      <c r="B214" t="s">
-        <v>11</v>
-      </c>
-      <c r="C214" t="s">
-        <v>757</v>
-      </c>
-      <c r="D214" t="s">
-        <v>758</v>
-      </c>
-      <c r="E214" t="s">
-        <v>750</v>
-      </c>
-      <c r="F214" t="s">
-        <v>15</v>
-      </c>
-      <c r="G214" t="s">
-        <v>16</v>
-      </c>
-      <c r="H214" t="s">
-        <v>16</v>
-      </c>
-      <c r="I214" t="s">
-        <v>16</v>
-      </c>
-      <c r="J214" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A215" t="s">
-        <v>759</v>
-      </c>
-      <c r="B215" t="s">
-        <v>11</v>
-      </c>
-      <c r="C215" t="s">
-        <v>760</v>
-      </c>
-      <c r="D215" t="s">
-        <v>761</v>
-      </c>
-      <c r="E215" t="s">
-        <v>750</v>
-      </c>
-      <c r="F215" t="s">
-        <v>15</v>
-      </c>
-      <c r="G215" t="s">
-        <v>16</v>
-      </c>
-      <c r="H215" t="s">
-        <v>16</v>
-      </c>
-      <c r="I215" t="s">
-        <v>16</v>
-      </c>
-      <c r="J215" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A216" t="s">
-        <v>762</v>
-      </c>
-      <c r="B216" t="s">
-        <v>11</v>
-      </c>
-      <c r="C216" t="s">
-        <v>763</v>
-      </c>
-      <c r="D216" t="s">
-        <v>764</v>
-      </c>
-      <c r="E216" t="s">
-        <v>750</v>
-      </c>
-      <c r="F216" t="s">
-        <v>15</v>
-      </c>
-      <c r="G216" t="s">
-        <v>16</v>
-      </c>
-      <c r="H216" t="s">
-        <v>16</v>
-      </c>
-      <c r="I216" t="s">
-        <v>16</v>
-      </c>
-      <c r="J216" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A217" t="s">
-        <v>765</v>
-      </c>
-      <c r="B217" t="s">
-        <v>11</v>
-      </c>
-      <c r="C217" t="s">
-        <v>766</v>
-      </c>
-      <c r="D217" t="s">
-        <v>767</v>
-      </c>
-      <c r="E217" t="s">
-        <v>750</v>
-      </c>
-      <c r="F217" t="s">
-        <v>15</v>
-      </c>
-      <c r="G217" t="s">
-        <v>16</v>
-      </c>
-      <c r="H217" t="s">
-        <v>16</v>
-      </c>
-      <c r="I217" t="s">
-        <v>16</v>
-      </c>
-      <c r="J217" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A218" t="s">
-        <v>768</v>
-      </c>
-      <c r="B218" t="s">
-        <v>11</v>
-      </c>
-      <c r="C218" t="s">
-        <v>769</v>
-      </c>
-      <c r="D218" t="s">
-        <v>770</v>
-      </c>
-      <c r="E218" t="s">
-        <v>750</v>
-      </c>
-      <c r="F218" t="s">
-        <v>15</v>
-      </c>
-      <c r="G218" t="s">
-        <v>16</v>
-      </c>
-      <c r="H218" t="s">
-        <v>16</v>
-      </c>
-      <c r="I218" t="s">
-        <v>16</v>
-      </c>
-      <c r="J218" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A219" t="s">
-        <v>771</v>
-      </c>
-      <c r="B219" t="s">
-        <v>11</v>
-      </c>
-      <c r="C219" t="s">
-        <v>772</v>
-      </c>
-      <c r="D219" t="s">
-        <v>773</v>
-      </c>
-      <c r="E219" t="s">
-        <v>750</v>
-      </c>
-      <c r="F219" t="s">
-        <v>15</v>
-      </c>
-      <c r="G219" t="s">
-        <v>16</v>
-      </c>
-      <c r="H219" t="s">
-        <v>16</v>
-      </c>
-      <c r="I219" t="s">
-        <v>16</v>
-      </c>
-      <c r="J219" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A220" t="s">
-        <v>774</v>
-      </c>
-      <c r="B220" t="s">
-        <v>11</v>
-      </c>
-      <c r="C220" t="s">
-        <v>775</v>
-      </c>
-      <c r="D220" t="s">
-        <v>776</v>
-      </c>
-      <c r="E220" t="s">
-        <v>750</v>
-      </c>
-      <c r="F220" t="s">
-        <v>15</v>
-      </c>
-      <c r="G220" t="s">
-        <v>16</v>
-      </c>
-      <c r="H220" t="s">
-        <v>16</v>
-      </c>
-      <c r="I220" t="s">
-        <v>16</v>
-      </c>
-      <c r="J220" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A221" t="s">
-        <v>777</v>
-      </c>
-      <c r="B221" t="s">
-        <v>11</v>
-      </c>
-      <c r="C221" t="s">
-        <v>778</v>
-      </c>
-      <c r="D221" t="s">
-        <v>779</v>
-      </c>
-      <c r="E221" t="s">
-        <v>750</v>
-      </c>
-      <c r="F221" t="s">
-        <v>15</v>
-      </c>
-      <c r="G221" t="s">
-        <v>16</v>
-      </c>
-      <c r="H221" t="s">
-        <v>16</v>
-      </c>
-      <c r="I221" t="s">
-        <v>16</v>
-      </c>
-      <c r="J221" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A222" t="s">
-        <v>780</v>
-      </c>
-      <c r="B222" t="s">
-        <v>11</v>
-      </c>
-      <c r="C222" t="s">
-        <v>781</v>
-      </c>
-      <c r="D222" t="s">
-        <v>782</v>
-      </c>
-      <c r="E222" t="s">
-        <v>750</v>
-      </c>
-      <c r="F222" t="s">
-        <v>15</v>
-      </c>
-      <c r="G222" t="s">
-        <v>16</v>
-      </c>
-      <c r="H222" t="s">
-        <v>16</v>
-      </c>
-      <c r="I222" t="s">
-        <v>16</v>
-      </c>
-      <c r="J222" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="223" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A223" t="s">
-        <v>783</v>
-      </c>
-      <c r="B223" t="s">
-        <v>11</v>
-      </c>
-      <c r="C223" t="s">
-        <v>784</v>
-      </c>
-      <c r="D223" t="s">
-        <v>785</v>
-      </c>
-      <c r="E223" t="s">
-        <v>750</v>
-      </c>
-      <c r="F223" t="s">
-        <v>15</v>
-      </c>
-      <c r="G223" t="s">
-        <v>16</v>
-      </c>
-      <c r="H223" t="s">
-        <v>16</v>
-      </c>
-      <c r="I223" t="s">
-        <v>16</v>
-      </c>
-      <c r="J223" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="224" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A224" t="s">
-        <v>786</v>
-      </c>
-      <c r="B224" t="s">
-        <v>11</v>
-      </c>
-      <c r="C224" t="s">
-        <v>787</v>
-      </c>
-      <c r="D224" t="s">
-        <v>788</v>
-      </c>
-      <c r="E224" t="s">
-        <v>750</v>
-      </c>
-      <c r="F224" t="s">
-        <v>15</v>
-      </c>
-      <c r="G224" t="s">
-        <v>16</v>
-      </c>
-      <c r="H224" t="s">
-        <v>16</v>
-      </c>
-      <c r="I224" t="s">
-        <v>16</v>
-      </c>
-      <c r="J224" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A225" t="s">
-        <v>789</v>
-      </c>
-      <c r="B225" t="s">
-        <v>11</v>
-      </c>
-      <c r="C225" t="s">
-        <v>790</v>
-      </c>
-      <c r="D225" t="s">
-        <v>791</v>
-      </c>
-      <c r="E225" t="s">
-        <v>750</v>
-      </c>
-      <c r="F225" t="s">
-        <v>15</v>
-      </c>
-      <c r="G225" t="s">
-        <v>16</v>
-      </c>
-      <c r="H225" t="s">
-        <v>16</v>
-      </c>
-      <c r="I225" t="s">
-        <v>16</v>
-      </c>
-      <c r="J225" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A226" t="s">
-        <v>792</v>
-      </c>
-      <c r="B226" t="s">
-        <v>11</v>
-      </c>
-      <c r="C226" t="s">
-        <v>793</v>
-      </c>
-      <c r="D226" t="s">
-        <v>794</v>
-      </c>
-      <c r="E226" t="s">
-        <v>750</v>
-      </c>
-      <c r="F226" t="s">
-        <v>15</v>
-      </c>
-      <c r="G226" t="s">
-        <v>16</v>
-      </c>
-      <c r="H226" t="s">
-        <v>16</v>
-      </c>
-      <c r="I226" t="s">
-        <v>16</v>
-      </c>
-      <c r="J226" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A227" t="s">
-        <v>795</v>
-      </c>
-      <c r="B227" t="s">
-        <v>11</v>
-      </c>
-      <c r="C227" t="s">
-        <v>796</v>
-      </c>
-      <c r="D227" t="s">
-        <v>797</v>
-      </c>
-      <c r="E227" t="s">
-        <v>750</v>
-      </c>
-      <c r="F227" t="s">
-        <v>15</v>
-      </c>
-      <c r="G227" t="s">
-        <v>16</v>
-      </c>
-      <c r="H227" t="s">
-        <v>16</v>
-      </c>
-      <c r="I227" t="s">
-        <v>16</v>
-      </c>
-      <c r="J227" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A228" t="s">
-        <v>798</v>
-      </c>
-      <c r="B228" t="s">
-        <v>11</v>
-      </c>
-      <c r="C228" t="s">
-        <v>799</v>
-      </c>
-      <c r="D228" t="s">
-        <v>800</v>
-      </c>
-      <c r="E228" t="s">
-        <v>750</v>
-      </c>
-      <c r="F228" t="s">
-        <v>15</v>
-      </c>
-      <c r="G228" t="s">
-        <v>16</v>
-      </c>
-      <c r="H228" t="s">
-        <v>16</v>
-      </c>
-      <c r="I228" t="s">
-        <v>16</v>
-      </c>
-      <c r="J228" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A229" t="s">
-        <v>801</v>
-      </c>
-      <c r="B229" t="s">
-        <v>11</v>
-      </c>
-      <c r="C229" t="s">
-        <v>802</v>
-      </c>
-      <c r="D229" t="s">
-        <v>803</v>
-      </c>
-      <c r="E229" t="s">
-        <v>750</v>
-      </c>
-      <c r="F229" t="s">
-        <v>15</v>
-      </c>
-      <c r="G229" t="s">
-        <v>16</v>
-      </c>
-      <c r="H229" t="s">
-        <v>16</v>
-      </c>
-      <c r="I229" t="s">
-        <v>16</v>
-      </c>
-      <c r="J229" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A230" t="s">
-        <v>804</v>
-      </c>
-      <c r="B230" t="s">
-        <v>11</v>
-      </c>
-      <c r="C230" t="s">
-        <v>805</v>
-      </c>
-      <c r="D230" t="s">
-        <v>806</v>
-      </c>
-      <c r="E230" t="s">
-        <v>750</v>
-      </c>
-      <c r="F230" t="s">
-        <v>15</v>
-      </c>
-      <c r="G230" t="s">
-        <v>16</v>
-      </c>
-      <c r="H230" t="s">
-        <v>16</v>
-      </c>
-      <c r="I230" t="s">
-        <v>16</v>
-      </c>
-      <c r="J230" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A231" t="s">
-        <v>807</v>
-      </c>
-      <c r="B231" t="s">
-        <v>11</v>
-      </c>
-      <c r="C231" t="s">
-        <v>808</v>
-      </c>
-      <c r="D231" t="s">
-        <v>809</v>
-      </c>
-      <c r="E231" t="s">
-        <v>750</v>
-      </c>
-      <c r="F231" t="s">
-        <v>15</v>
-      </c>
-      <c r="G231" t="s">
-        <v>16</v>
-      </c>
-      <c r="H231" t="s">
-        <v>16</v>
-      </c>
-      <c r="I231" t="s">
-        <v>16</v>
-      </c>
-      <c r="J231" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A232" t="s">
-        <v>810</v>
-      </c>
-      <c r="B232" t="s">
-        <v>11</v>
-      </c>
-      <c r="C232" t="s">
-        <v>811</v>
-      </c>
-      <c r="D232" t="s">
-        <v>812</v>
-      </c>
-      <c r="E232" t="s">
-        <v>750</v>
-      </c>
-      <c r="F232" t="s">
-        <v>15</v>
-      </c>
-      <c r="G232" t="s">
-        <v>16</v>
-      </c>
-      <c r="H232" t="s">
-        <v>16</v>
-      </c>
-      <c r="I232" t="s">
-        <v>16</v>
-      </c>
-      <c r="J232" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A233" t="s">
-        <v>813</v>
-      </c>
-      <c r="B233" t="s">
-        <v>11</v>
-      </c>
-      <c r="C233" t="s">
-        <v>814</v>
-      </c>
-      <c r="D233" t="s">
-        <v>815</v>
-      </c>
-      <c r="E233" t="s">
-        <v>750</v>
-      </c>
-      <c r="F233" t="s">
-        <v>15</v>
-      </c>
-      <c r="G233" t="s">
-        <v>16</v>
-      </c>
-      <c r="H233" t="s">
-        <v>16</v>
-      </c>
-      <c r="I233" t="s">
-        <v>16</v>
-      </c>
-      <c r="J233" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A234" t="s">
-        <v>816</v>
-      </c>
-      <c r="B234" t="s">
-        <v>11</v>
-      </c>
-      <c r="C234" t="s">
-        <v>817</v>
-      </c>
-      <c r="D234" t="s">
-        <v>818</v>
-      </c>
-      <c r="E234" t="s">
-        <v>750</v>
-      </c>
-      <c r="F234" t="s">
-        <v>15</v>
-      </c>
-      <c r="G234" t="s">
-        <v>16</v>
-      </c>
-      <c r="H234" t="s">
-        <v>16</v>
-      </c>
-      <c r="I234" t="s">
-        <v>16</v>
-      </c>
-      <c r="J234" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A235" t="s">
-        <v>819</v>
-      </c>
-      <c r="B235" t="s">
-        <v>11</v>
-      </c>
-      <c r="C235" t="s">
-        <v>820</v>
-      </c>
-      <c r="D235" t="s">
-        <v>821</v>
-      </c>
-      <c r="E235" t="s">
-        <v>750</v>
-      </c>
-      <c r="F235" t="s">
-        <v>15</v>
-      </c>
-      <c r="G235" t="s">
-        <v>16</v>
-      </c>
-      <c r="H235" t="s">
-        <v>16</v>
-      </c>
-      <c r="I235" t="s">
-        <v>16</v>
-      </c>
-      <c r="J235" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A236" t="s">
-        <v>822</v>
-      </c>
-      <c r="B236" t="s">
-        <v>11</v>
-      </c>
-      <c r="C236" t="s">
-        <v>823</v>
-      </c>
-      <c r="D236" t="s">
-        <v>824</v>
-      </c>
-      <c r="E236" t="s">
-        <v>750</v>
-      </c>
-      <c r="F236" t="s">
-        <v>15</v>
-      </c>
-      <c r="G236" t="s">
-        <v>16</v>
-      </c>
-      <c r="H236" t="s">
-        <v>16</v>
-      </c>
-      <c r="I236" t="s">
-        <v>16</v>
-      </c>
-      <c r="J236" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A237" t="s">
-        <v>825</v>
-      </c>
-      <c r="B237" t="s">
-        <v>11</v>
-      </c>
-      <c r="C237" t="s">
-        <v>826</v>
-      </c>
-      <c r="D237" t="s">
-        <v>827</v>
-      </c>
-      <c r="E237" t="s">
-        <v>828</v>
-      </c>
-      <c r="F237" t="s">
-        <v>15</v>
-      </c>
-      <c r="G237" t="s">
-        <v>16</v>
-      </c>
-      <c r="H237" t="s">
-        <v>16</v>
-      </c>
-      <c r="I237" t="s">
-        <v>16</v>
-      </c>
-      <c r="J237" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A238" t="s">
-        <v>829</v>
-      </c>
-      <c r="B238" t="s">
-        <v>11</v>
-      </c>
-      <c r="C238" t="s">
-        <v>830</v>
-      </c>
-      <c r="D238" t="s">
-        <v>831</v>
-      </c>
-      <c r="E238" t="s">
-        <v>828</v>
-      </c>
-      <c r="F238" t="s">
-        <v>15</v>
-      </c>
-      <c r="G238" t="s">
-        <v>16</v>
-      </c>
-      <c r="H238" t="s">
-        <v>16</v>
-      </c>
-      <c r="I238" t="s">
-        <v>16</v>
-      </c>
-      <c r="J238" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A239" t="s">
-        <v>832</v>
-      </c>
-      <c r="B239" t="s">
-        <v>11</v>
-      </c>
-      <c r="C239" t="s">
-        <v>833</v>
-      </c>
-      <c r="D239" t="s">
-        <v>834</v>
-      </c>
-      <c r="E239" t="s">
-        <v>828</v>
-      </c>
-      <c r="F239" t="s">
-        <v>15</v>
-      </c>
-      <c r="G239" t="s">
-        <v>16</v>
-      </c>
-      <c r="H239" t="s">
-        <v>16</v>
-      </c>
-      <c r="I239" t="s">
-        <v>16</v>
-      </c>
-      <c r="J239" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A240" t="s">
-        <v>835</v>
-      </c>
-      <c r="B240" t="s">
-        <v>11</v>
-      </c>
-      <c r="C240" t="s">
-        <v>836</v>
-      </c>
-      <c r="D240" t="s">
-        <v>837</v>
-      </c>
-      <c r="E240" t="s">
-        <v>828</v>
-      </c>
-      <c r="F240" t="s">
-        <v>15</v>
-      </c>
-      <c r="G240" t="s">
-        <v>16</v>
-      </c>
-      <c r="H240" t="s">
-        <v>16</v>
-      </c>
-      <c r="I240" t="s">
-        <v>16</v>
-      </c>
-      <c r="J240" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A241" t="s">
-        <v>838</v>
-      </c>
-      <c r="B241" t="s">
-        <v>11</v>
-      </c>
-      <c r="C241" t="s">
-        <v>839</v>
-      </c>
-      <c r="D241" t="s">
-        <v>840</v>
-      </c>
-      <c r="E241" t="s">
-        <v>828</v>
-      </c>
-      <c r="F241" t="s">
-        <v>15</v>
-      </c>
-      <c r="G241" t="s">
-        <v>16</v>
-      </c>
-      <c r="H241" t="s">
-        <v>16</v>
-      </c>
-      <c r="I241" t="s">
-        <v>16</v>
-      </c>
-      <c r="J241" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A242" t="s">
-        <v>841</v>
-      </c>
-      <c r="B242" t="s">
-        <v>11</v>
-      </c>
-      <c r="C242" t="s">
-        <v>842</v>
-      </c>
-      <c r="D242" t="s">
-        <v>843</v>
-      </c>
-      <c r="E242" t="s">
-        <v>828</v>
-      </c>
-      <c r="F242" t="s">
-        <v>15</v>
-      </c>
-      <c r="G242" t="s">
-        <v>16</v>
-      </c>
-      <c r="H242" t="s">
-        <v>16</v>
-      </c>
-      <c r="I242" t="s">
-        <v>16</v>
-      </c>
-      <c r="J242" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A243" t="s">
-        <v>844</v>
-      </c>
-      <c r="B243" t="s">
-        <v>11</v>
-      </c>
-      <c r="C243" t="s">
-        <v>845</v>
-      </c>
-      <c r="D243" t="s">
-        <v>846</v>
-      </c>
-      <c r="E243" t="s">
-        <v>828</v>
-      </c>
-      <c r="F243" t="s">
-        <v>15</v>
-      </c>
-      <c r="G243" t="s">
-        <v>16</v>
-      </c>
-      <c r="H243" t="s">
-        <v>16</v>
-      </c>
-      <c r="I243" t="s">
-        <v>16</v>
-      </c>
-      <c r="J243" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A244" t="s">
-        <v>847</v>
-      </c>
-      <c r="B244" t="s">
-        <v>11</v>
-      </c>
-      <c r="C244" t="s">
-        <v>848</v>
-      </c>
-      <c r="D244" t="s">
-        <v>849</v>
-      </c>
-      <c r="E244" t="s">
-        <v>828</v>
-      </c>
-      <c r="F244" t="s">
-        <v>15</v>
-      </c>
-      <c r="G244" t="s">
-        <v>16</v>
-      </c>
-      <c r="H244" t="s">
-        <v>16</v>
-      </c>
-      <c r="I244" t="s">
-        <v>16</v>
-      </c>
-      <c r="J244" t="s">
-        <v>755</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J244" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J244" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J211" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10843,90 +9478,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="92.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
-        <v>850</v>
+        <v>747</v>
       </c>
       <c r="B1" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>852</v>
+        <v>749</v>
       </c>
       <c r="B2" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>854</v>
+        <v>751</v>
       </c>
       <c r="B3" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>856</v>
+        <v>753</v>
       </c>
       <c r="B4" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>858</v>
+        <v>755</v>
       </c>
       <c r="B5" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>860</v>
+        <v>757</v>
       </c>
       <c r="B6" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>759</v>
       </c>
       <c r="B7" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>864</v>
+        <v>761</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>865</v>
+        <v>762</v>
       </c>
       <c r="B9" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>867</v>
+        <v>764</v>
       </c>
       <c r="B10" t="s">
-        <v>868</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>
